--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484299_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484299_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8016</v>
+        <v>8.2821</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5284</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2732</v>
+        <v>0.1721</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0738</v>
+        <v>8.1029</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0353</v>
+        <v>1.3855</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0385</v>
+        <v>6.7173</v>
       </c>
       <c r="J2" t="n">
-        <v>2.778</v>
+        <v>10.3646</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3341</v>
+        <v>2.7027</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4439</v>
+        <v>7.6618</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7042</v>
+        <v>-2.2617</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2988</v>
+        <v>-1.3172</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4054</v>
+        <v>-0.9445</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6651</v>
+        <v>-0.0825</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1594</v>
+        <v>-0.3012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8246</v>
+        <v>0.2186</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4999</v>
+        <v>0.0664</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.3947</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5392</v>
+        <v>7.4397</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5033</v>
+        <v>4.6295</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0359</v>
+        <v>2.8102</v>
       </c>
       <c r="G3" t="n">
-        <v>8.1029</v>
+        <v>2.0738</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3855</v>
+        <v>1.0353</v>
       </c>
       <c r="I3" t="n">
-        <v>6.7173</v>
+        <v>1.0385</v>
       </c>
       <c r="J3" t="n">
-        <v>10.3646</v>
+        <v>2.778</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7027</v>
+        <v>1.3341</v>
       </c>
       <c r="L3" t="n">
-        <v>7.6618</v>
+        <v>1.4439</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2617</v>
+        <v>-0.7042</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3172</v>
+        <v>-0.2988</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9445</v>
+        <v>-0.4054</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8254</v>
+        <v>0.3032</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.0583</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0824</v>
+        <v>0.3616</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0664</v>
+        <v>3.4999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0664</v>
+        <v>1.3947</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6023</v>
+        <v>5.2718</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1535</v>
+        <v>2.8501</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4489</v>
+        <v>2.4216</v>
       </c>
       <c r="G4" t="n">
         <v>3.2164</v>
@@ -766,13 +766,13 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3822</v>
+        <v>1.0516</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6962</v>
+        <v>0.3929</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.2224</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1798</v>
+        <v>3.382</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3087</v>
+        <v>2.5109</v>
       </c>
       <c r="F5" t="n">
         <v>0.8711</v>
@@ -844,10 +844,10 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4182</v>
+        <v>-0.216</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1761</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5192</v>
+        <v>2.173</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4174</v>
+        <v>1.3163</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1019</v>
+        <v>0.8568</v>
       </c>
       <c r="G6" t="n">
         <v>3.0218</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.4285</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1294</v>
+        <v>0.0283</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6453</v>
+        <v>0.4002</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8865</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4809</v>
+        <v>1.2889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7754</v>
+        <v>3.8889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7055</v>
+        <v>-2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9009</v>
+        <v>1.9239</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4694</v>
+        <v>0.2648</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4315</v>
+        <v>1.6591</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1619</v>
+        <v>5.0595</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>2.6036</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7391</v>
+        <v>-3.1356</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4694</v>
+        <v>-2.1911</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2696</v>
+        <v>-0.9445</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1893</v>
+        <v>0.3219</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6136</v>
+        <v>-0.1939</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4243</v>
+        <v>0.5158</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4639</v>
+        <v>1.1582</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0911</v>
+        <v>0.371</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6272</v>
+        <v>0.7872</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9239</v>
+        <v>0.9009</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2648</v>
+        <v>0.4694</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6591</v>
+        <v>0.4315</v>
       </c>
       <c r="J8" t="n">
-        <v>5.0595</v>
+        <v>0.1619</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6036</v>
+        <v>0.1619</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1356</v>
+        <v>0.7391</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1911</v>
+        <v>0.4694</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9445</v>
+        <v>0.2696</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4969</v>
+        <v>-0.1335</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0083</v>
+        <v>0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4886</v>
+        <v>-0.3426</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1522</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6763</v>
+        <v>0.8397</v>
       </c>
       <c r="E9" t="n">
         <v>-1.236</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9123</v>
+        <v>2.0758</v>
       </c>
       <c r="G9" t="n">
         <v>0.9466</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>0.351</v>
+        <v>0.5144</v>
       </c>
       <c r="T9" t="n">
         <v>0.1432</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2079</v>
+        <v>0.3713</v>
       </c>
       <c r="V9" t="n">
         <v>0.9414</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2921</v>
+        <v>-0.7269</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9442</v>
+        <v>0.0342</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6521</v>
+        <v>-0.7611</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2747</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1175</v>
+        <v>1.0985</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4171</v>
+        <v>0.507</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7004</v>
+        <v>0.5915</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5507</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5979</v>
+        <v>-1.1002</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9813</v>
+        <v>-2.3746</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3834</v>
+        <v>1.2744</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1338</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0401</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2888</v>
+        <v>0.3179</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3289</v>
+        <v>0.22</v>
       </c>
       <c r="V11" t="n">
         <v>0.2772</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8117</v>
+        <v>-1.9759</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5375</v>
+        <v>-1.1328</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2742</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3187</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1433</v>
+        <v>-1.1195</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1755</v>
+        <v>0.1623</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2027</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4339</v>
+        <v>0.3927</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7688</v>
+        <v>0.5675</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5215</v>
+        <v>-1.9174</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5771</v>
+        <v>-1.5121</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9443</v>
+        <v>-0.4052</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>0.394</v>
+        <v>0.5125</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1899</v>
+        <v>0.0558</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2041</v>
+        <v>0.4566</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0664</v>
+        <v>-0.5545</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0664</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1195</v>
+        <v>-2.0606</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8406</v>
+        <v>-0.8408</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2789</v>
+        <v>-1.2198</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.3187</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1195</v>
+        <v>-0.1433</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1623</v>
+        <v>-0.1755</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9602000000000001</v>
+        <v>2.2027</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3927</v>
+        <v>1.4339</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5675</v>
+        <v>0.7688</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9174</v>
+        <v>-2.5215</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5121</v>
+        <v>-1.5771</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4052</v>
+        <v>-0.9443</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6311</v>
+        <v>0.1452</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.652</v>
+        <v>-0.1134</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0209</v>
+        <v>0.2586</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5545</v>
+        <v>0.0664</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5545</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.02620000000001</v>
+        <v>23.9718</v>
       </c>
       <c r="E14" t="n">
-        <v>18.1266</v>
+        <v>18.1267</v>
       </c>
       <c r="F14" t="n">
-        <v>5.899799999999999</v>
+        <v>5.8451</v>
       </c>
       <c r="G14" t="n">
         <v>20.4474</v>
@@ -1531,7 +1531,7 @@
         <v>-9.496600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.524</v>
+        <v>-6.523999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-2.9726</v>
@@ -1546,16 +1546,16 @@
         <v>12.6973</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5361</v>
+        <v>4.4816</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9475999999999999</v>
+        <v>0.9475000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5887</v>
+        <v>3.5343</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9962000000000002</v>
+        <v>0.9961999999999998</v>
       </c>
       <c r="W14" t="n">
         <v>1.8857</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0428</v>
+        <v>-0.0955</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0338</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.0766</v>
+        <v>-0.6837</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1469</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5958</v>
+        <v>-0.3372</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5511</v>
+        <v>0.2564</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8314</v>
+        <v>1.7664</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3354</v>
+        <v>1.1051</v>
       </c>
       <c r="L15" t="n">
-        <v>2.496</v>
+        <v>0.6613</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.9783</v>
+        <v>-1.8472</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9312</v>
+        <v>-1.4423</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.0472</v>
+        <v>-0.4049</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8186</v>
+        <v>-0.2882</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5698</v>
+        <v>-0.2015</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2489</v>
+        <v>-0.0867</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8865</v>
+        <v>0.6642</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3872</v>
+        <v>-0.6897</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4871</v>
+        <v>-1.0683</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8743</v>
+        <v>0.3786</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.4063</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3372</v>
+        <v>-0.4876</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2564</v>
+        <v>0.0813</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7664</v>
+        <v>0.0081</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1051</v>
+        <v>0.0614</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6613</v>
+        <v>-0.0533</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8472</v>
+        <v>-0.4144</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4423</v>
+        <v>-0.549</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4049</v>
+        <v>0.1346</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.58</v>
+        <v>-0.2015</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3026</v>
+        <v>-0.0997</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2774</v>
+        <v>-0.1018</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1353</v>
+        <v>-1.1432</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1092</v>
+        <v>0.2103</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2446</v>
+        <v>-1.3535</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7422</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1745</v>
+        <v>-0.1823</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6052</v>
+        <v>-0.5041</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4308</v>
+        <v>0.3218</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1952</v>
+        <v>-1.2616</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5738</v>
+        <v>3.2248</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3786</v>
+        <v>-4.4865</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4063</v>
+        <v>-2.1469</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4876</v>
+        <v>-0.5958</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0813</v>
+        <v>-1.5511</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0081</v>
+        <v>3.8314</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0614</v>
+        <v>1.3354</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0533</v>
+        <v>2.496</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4144</v>
+        <v>-5.9783</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.549</v>
+        <v>-1.9312</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1346</v>
+        <v>-4.0472</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7071</v>
+        <v>0.5998</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6052</v>
+        <v>-0.2392</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1018</v>
+        <v>0.839</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2275</v>
+        <v>-1.462</v>
       </c>
       <c r="E19" t="n">
-        <v>0.697</v>
+        <v>0.1914</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9245</v>
+        <v>-1.6535</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5205</v>
@@ -1936,13 +1936,13 @@
         <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1292</v>
+        <v>-0.3638</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3882</v>
+        <v>-0.1174</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5174</v>
+        <v>-0.2464</v>
       </c>
       <c r="V19" t="n">
         <v>0.0549</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2854</v>
+        <v>-1.4955</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1014</v>
+        <v>-1.2026</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.184</v>
+        <v>-0.2929</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0136</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.389</v>
+        <v>-0.5991</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1127</v>
+        <v>-0.2138</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2763</v>
+        <v>-0.3853</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6642</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5004</v>
+        <v>-2.4552</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6408</v>
+        <v>-1.4075</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8597</v>
+        <v>-1.0477</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1846</v>
+        <v>-1.733</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8046</v>
+        <v>0.0205</v>
       </c>
       <c r="I21" t="n">
-        <v>0.62</v>
+        <v>-1.7534</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4908</v>
+        <v>-0.6536</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5718</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6937</v>
+        <v>-1.0793</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2328</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>-1.0793</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6795</v>
+        <v>0.2545</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1732</v>
+        <v>0.2229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5063</v>
+        <v>0.0316</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7779</v>
+        <v>-2.5004</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8119</v>
+        <v>-1.6408</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.966</v>
+        <v>-0.8597</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.733</v>
+        <v>-1.1846</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0205</v>
+        <v>-1.8046</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7534</v>
+        <v>0.62</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6536</v>
+        <v>-0.4908</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0205</v>
+        <v>-0.5718</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0793</v>
+        <v>-0.6937</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-1.2328</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0793</v>
+        <v>0.5391</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0682</v>
+        <v>-0.6795</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1816</v>
+        <v>-0.1732</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1133</v>
+        <v>-0.5063</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1121</v>
+        <v>-3.5996</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8044</v>
+        <v>-1.2088</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3077</v>
+        <v>-2.3908</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2088</v>
@@ -2248,13 +2248,13 @@
         <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7572</v>
+        <v>0.2696</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1983</v>
+        <v>-0.2062</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5589</v>
+        <v>0.4758</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4366</v>
+        <v>-3.9828</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1581</v>
+        <v>-3.057</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2785</v>
+        <v>-0.9258</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6852</v>
@@ -2326,13 +2326,13 @@
         <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4697</v>
+        <v>-1.0158</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.839</v>
+        <v>-0.7379</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6307</v>
+        <v>-0.278</v>
       </c>
       <c r="V24" t="n">
         <v>0.4996</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2216</v>
+        <v>-4.9626</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5327</v>
+        <v>-0.9261</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.6889</v>
+        <v>-4.0366</v>
       </c>
       <c r="G25" t="n">
         <v>-3.5546</v>
@@ -2404,13 +2404,13 @@
         <v>1.7581</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3815</v>
+        <v>-1.1225</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5131</v>
+        <v>-0.9064</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.2161</v>
       </c>
       <c r="V25" t="n">
         <v>0.8865</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-24.322</v>
+        <v>-23.6481</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.296</v>
+        <v>-6.2964</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.0262</v>
+        <v>-17.3521</v>
       </c>
       <c r="G26" t="n">
         <v>-21.2764</v>
@@ -2482,13 +2482,13 @@
         <v>14.6509</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0029</v>
+        <v>-3.3288</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.176299999999999</v>
+        <v>-3.1765</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8263999999999999</v>
+        <v>-0.1523999999999998</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9962000000000003</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484299_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484299_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>1.3947</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0.3321</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,11 +1628,12 @@
       <c r="X14" t="n">
         <v>-0.8894999999999996</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0955</v>
+        <v>1.521</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5881999999999999</v>
+        <v>1.521</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6837</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.08069999999999999</v>
+        <v>1.521</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3372</v>
+        <v>0.307</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2564</v>
+        <v>1.214</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7664</v>
+        <v>1.521</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1051</v>
+        <v>0.307</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6613</v>
+        <v>1.214</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8472</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4423</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2882</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2015</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0867</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6897</v>
+        <v>0.307</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0683</v>
+        <v>0.307</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3786</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4063</v>
+        <v>0.307</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4876</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0813</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0081</v>
+        <v>0.307</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0614</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4144</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.549</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2015</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0997</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1018</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1432</v>
+        <v>-0.0955</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2103</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3535</v>
+        <v>-0.6837</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7422</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8248</v>
+        <v>-0.3372</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9175</v>
+        <v>0.2564</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7144</v>
+        <v>1.7664</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5526</v>
+        <v>1.1051</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1619</v>
+        <v>0.6613</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4567</v>
+        <v>-1.8472</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3773</v>
+        <v>-1.4423</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0793</v>
+        <v>-0.4049</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1823</v>
+        <v>-0.2882</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5041</v>
+        <v>-0.2015</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3218</v>
+        <v>-0.0867</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2616</v>
+        <v>-0.6897</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2248</v>
+        <v>-1.0683</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4865</v>
+        <v>0.3786</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1469</v>
+        <v>-0.4063</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5958</v>
+        <v>-0.4876</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5511</v>
+        <v>0.0813</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8314</v>
+        <v>0.0081</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3354</v>
+        <v>0.0614</v>
       </c>
       <c r="L18" t="n">
-        <v>2.496</v>
+        <v>-0.0533</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.9783</v>
+        <v>-0.4144</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9312</v>
+        <v>-0.549</v>
       </c>
       <c r="O18" t="n">
-        <v>-4.0472</v>
+        <v>0.1346</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5998</v>
+        <v>-0.2015</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2392</v>
+        <v>-0.0997</v>
       </c>
       <c r="U18" t="n">
-        <v>0.839</v>
+        <v>-0.1018</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.462</v>
+        <v>-1.2616</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1914</v>
+        <v>3.2248</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6535</v>
+        <v>-4.4865</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5205</v>
+        <v>-2.1469</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6411</v>
+        <v>-0.5958</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1206</v>
+        <v>-1.5511</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2855</v>
+        <v>3.8314</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2638</v>
+        <v>1.3354</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5493</v>
+        <v>2.496</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8061</v>
+        <v>-5.9783</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3773</v>
+        <v>-1.9312</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4287</v>
+        <v>-4.0472</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3638</v>
+        <v>0.5998</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1174</v>
+        <v>-0.2392</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2464</v>
+        <v>0.839</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0549</v>
+        <v>-0.8865</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0549</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +2060,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4955</v>
+        <v>-1.4502</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2026</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2929</v>
+        <v>-1.3535</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0136</v>
+        <v>-2.0492</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.229</v>
+        <v>-1.1317</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2154</v>
+        <v>-0.9175</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3246</v>
+        <v>0.4075</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4055</v>
+        <v>0.2456</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>0.1619</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6891</v>
+        <v>-2.4567</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8235</v>
+        <v>-1.3773</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1344</v>
+        <v>-1.0793</v>
       </c>
       <c r="P20" t="n">
         <v>0.7814</v>
@@ -2014,28 +2105,33 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5991</v>
+        <v>-0.1823</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2138</v>
+        <v>-0.5041</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3853</v>
+        <v>0.3218</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4552</v>
+        <v>-1.4955</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4075</v>
+        <v>-1.2026</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0477</v>
+        <v>-0.2929</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.733</v>
+        <v>-1.0136</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0205</v>
+        <v>-1.229</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7534</v>
+        <v>0.2154</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6536</v>
+        <v>-0.3246</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>-0.4055</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0793</v>
+        <v>-0.6891</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.8235</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0793</v>
+        <v>0.1344</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2545</v>
+        <v>-0.5991</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2229</v>
+        <v>-0.2138</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0316</v>
+        <v>-0.3853</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5004</v>
+        <v>-2.4552</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6408</v>
+        <v>-1.4075</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8597</v>
+        <v>-1.0477</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1846</v>
+        <v>-1.733</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8046</v>
+        <v>0.0205</v>
       </c>
       <c r="I22" t="n">
-        <v>0.62</v>
+        <v>-1.7534</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4908</v>
+        <v>-0.6536</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5718</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6937</v>
+        <v>-1.0793</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2328</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5391</v>
+        <v>-1.0793</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6795</v>
+        <v>0.2545</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1732</v>
+        <v>0.2229</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5063</v>
+        <v>0.0316</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5996</v>
+        <v>-2.5004</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2088</v>
+        <v>-1.6408</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3908</v>
+        <v>-0.8597</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.2088</v>
+        <v>-1.1846</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9039</v>
+        <v>-1.8046</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.305</v>
+        <v>0.62</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4159</v>
+        <v>-0.4908</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8875999999999999</v>
+        <v>-0.5718</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4718</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.6247</v>
+        <v>-0.6937</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7915</v>
+        <v>-1.2328</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.8332</v>
+        <v>0.5391</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2696</v>
+        <v>-0.6795</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2062</v>
+        <v>-0.1732</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4758</v>
+        <v>-0.5063</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4418</v>
+        <v>-0.8317</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9828</v>
+        <v>-2.983</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.057</v>
+        <v>-1.3295</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9258</v>
+        <v>-1.6535</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6852</v>
+        <v>-4.0415</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9394</v>
+        <v>-2.9481</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.6245</v>
+        <v>-1.0934</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1114</v>
+        <v>-0.2354</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5214</v>
+        <v>-1.5708</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.41</v>
+        <v>1.3354</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7966</v>
+        <v>-3.8061</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.582</v>
+        <v>-1.3773</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2146</v>
+        <v>-2.4287</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0158</v>
+        <v>-0.3638</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7379</v>
+        <v>-0.1174</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.278</v>
+        <v>-0.2464</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4996</v>
+        <v>0.0549</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9626</v>
+        <v>-3.5996</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9261</v>
+        <v>-1.2088</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.0366</v>
+        <v>-2.3908</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5546</v>
+        <v>-4.2088</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5986</v>
+        <v>-0.9039</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.956</v>
+        <v>-3.305</v>
       </c>
       <c r="J25" t="n">
-        <v>2.0239</v>
+        <v>0.4159</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7418</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2821</v>
+        <v>-0.4718</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.5785</v>
+        <v>-4.6247</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.3405</v>
+        <v>-1.7915</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.238</v>
+        <v>-2.8332</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R25" t="n">
         <v>1.7581</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1225</v>
+        <v>0.2696</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9064</v>
+        <v>-0.2062</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2161</v>
+        <v>0.4758</v>
       </c>
       <c r="V25" t="n">
-        <v>0.8865</v>
+        <v>-0.4418</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8865</v>
+        <v>-0.4418</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-3.9828</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.057</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.9258</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.6852</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.9394</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-4.6245</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.5214</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.7966</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.582</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.0158</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.7379</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. MARTIN TRENADO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.9626</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.9261</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-4.0366</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.5546</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.5986</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.956</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.0239</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-5.5785</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-2.3405</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-3.238</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-1.1225</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.9064</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2161</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484299_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-23.6481</v>
       </c>
-      <c r="E26" t="n">
-        <v>-6.2964</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E28" t="n">
+        <v>-6.2963</v>
+      </c>
+      <c r="F28" t="n">
         <v>-17.3521</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>-21.2764</v>
       </c>
-      <c r="H26" t="n">
-        <v>-8.4627</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="H28" t="n">
+        <v>-8.4626</v>
+      </c>
+      <c r="I28" t="n">
         <v>-12.8138</v>
       </c>
-      <c r="J26" t="n">
-        <v>8.687999999999999</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J28" t="n">
+        <v>8.688199999999998</v>
+      </c>
+      <c r="K28" t="n">
         <v>5.9847</v>
       </c>
-      <c r="L26" t="n">
-        <v>2.703200000000001</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="L28" t="n">
+        <v>2.7033</v>
+      </c>
+      <c r="M28" t="n">
         <v>-29.9646</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>-14.4474</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>-15.5171</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>1.9534</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>14.6509</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>-3.3288</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>-3.1765</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>-0.1523999999999998</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V28" t="n">
         <v>-0.9962000000000003</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>0.8893999999999999</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-1.8857</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
